--- a/assets/Products.xlsx
+++ b/assets/Products.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="65">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -132,6 +133,90 @@
   </si>
   <si>
     <t xml:space="preserve">Solvent Recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIN_STEP_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNAMIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Instructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line Clearance Checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line Clearance Record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material List</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line Clearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulverization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extraction Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blow Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blow Off Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semi Concentration Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Concentration Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying Chart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager Signoff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Concentration &amp; TDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentration Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line clearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spray Drying chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spray Drying Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtration Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethanol Stripout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying chart</t>
   </si>
 </sst>
 </file>
@@ -178,12 +263,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -263,7 +354,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -277,10 +368,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -352,6 +439,42 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,7 +505,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFBBE6FE"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -618,8 +741,8 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="34.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="34.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="16.27"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="4" width="11.53"/>
   </cols>
   <sheetData>
@@ -635,1488 +758,2785 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="15"/>
+      <c r="B69" s="14"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="15"/>
+      <c r="B70" s="14"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="15"/>
+      <c r="B72" s="14"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="15"/>
+      <c r="B73" s="14"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="15"/>
+      <c r="B74" s="14"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="15"/>
+      <c r="B75" s="14"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="15"/>
+      <c r="B76" s="14"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="15"/>
+      <c r="B77" s="14"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="17"/>
+      <c r="B79" s="16"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="17"/>
+      <c r="B80" s="16"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="17"/>
+      <c r="B81" s="16"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="17"/>
+      <c r="B82" s="16"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="17"/>
+      <c r="B83" s="16"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="17"/>
+      <c r="B84" s="16"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="17"/>
+      <c r="B85" s="16"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="17"/>
+      <c r="B86" s="16"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="17"/>
+      <c r="B87" s="16"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="17"/>
+      <c r="B88" s="16"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="17"/>
+      <c r="B89" s="16"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="17"/>
+      <c r="B90" s="16"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="17"/>
+      <c r="B91" s="16"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="17"/>
+      <c r="B92" s="16"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="17"/>
+      <c r="B93" s="16"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="17"/>
+      <c r="B94" s="16"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="17"/>
+      <c r="B95" s="16"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="17"/>
+      <c r="B96" s="16"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="17"/>
+      <c r="B97" s="16"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="17"/>
+      <c r="B98" s="16"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="17"/>
+      <c r="B99" s="16"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="17"/>
+      <c r="B100" s="16"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="17"/>
+      <c r="B101" s="16"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="17"/>
+      <c r="B102" s="16"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="17"/>
+      <c r="B103" s="16"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="17"/>
+      <c r="B104" s="16"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="17"/>
+      <c r="B105" s="16"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="18"/>
+      <c r="B106" s="17"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="15"/>
+      <c r="B108" s="14"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="15"/>
+      <c r="B109" s="14"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="15"/>
+      <c r="B110" s="14"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="15"/>
+      <c r="B111" s="14"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="15"/>
+      <c r="B112" s="14"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="15"/>
+      <c r="B113" s="14"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="15"/>
+      <c r="B114" s="14"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="15"/>
+      <c r="B115" s="14"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="15"/>
+      <c r="B116" s="14"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="15"/>
+      <c r="B117" s="14"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="15"/>
+      <c r="B118" s="14"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="15"/>
+      <c r="B119" s="14"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="15"/>
+      <c r="B120" s="14"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="15"/>
+      <c r="B121" s="14"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="15"/>
+      <c r="B122" s="14"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="15"/>
+      <c r="B123" s="14"/>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="15"/>
+      <c r="B124" s="14"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="15"/>
+      <c r="B125" s="14"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="15"/>
+      <c r="B126" s="14"/>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="15"/>
+      <c r="B127" s="14"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="15"/>
+      <c r="B128" s="14"/>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="15"/>
+      <c r="B129" s="14"/>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="15"/>
+      <c r="B130" s="14"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="15"/>
+      <c r="B131" s="14"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="15"/>
+      <c r="B132" s="14"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="15"/>
+      <c r="B133" s="14"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="15"/>
+      <c r="B134" s="14"/>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="15"/>
+      <c r="B135" s="14"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="15"/>
+      <c r="B136" s="14"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="15"/>
+      <c r="B137" s="14"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="15"/>
+      <c r="B138" s="14"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="15"/>
+      <c r="B139" s="14"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="15"/>
+      <c r="B140" s="14"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="15"/>
+      <c r="B141" s="14"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="15"/>
+      <c r="B142" s="14"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="15"/>
+      <c r="B143" s="14"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="15"/>
+      <c r="B144" s="14"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="15"/>
+      <c r="B145" s="14"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="15"/>
+      <c r="B146" s="14"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="19"/>
+      <c r="B148" s="18"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="19"/>
+      <c r="B149" s="18"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="19"/>
+      <c r="B150" s="18"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="19"/>
+      <c r="B151" s="18"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="19"/>
+      <c r="B152" s="18"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="19"/>
+      <c r="B153" s="18"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="19"/>
+      <c r="B154" s="18"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="19"/>
+      <c r="B155" s="18"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="19"/>
+      <c r="B156" s="18"/>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="19"/>
+      <c r="B157" s="18"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="19"/>
+      <c r="B158" s="18"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="19"/>
+      <c r="B160" s="18"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="19"/>
+      <c r="B161" s="18"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="19"/>
+      <c r="B162" s="18"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="19"/>
+      <c r="B163" s="18"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="19"/>
+      <c r="B164" s="18"/>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="19"/>
+      <c r="B165" s="18"/>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="19"/>
+      <c r="B166" s="18"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="19"/>
+      <c r="B167" s="18"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="19"/>
+      <c r="B168" s="18"/>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="19"/>
+      <c r="B169" s="18"/>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="19"/>
+      <c r="B170" s="18"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="19"/>
+      <c r="B171" s="18"/>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="19"/>
+      <c r="B173" s="18"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="19"/>
+      <c r="B174" s="18"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="19"/>
+      <c r="B175" s="18"/>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="19"/>
+      <c r="B176" s="18"/>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="19"/>
+      <c r="B177" s="18"/>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="19"/>
+      <c r="B178" s="18"/>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="19"/>
+      <c r="B179" s="18"/>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="19"/>
+      <c r="B180" s="18"/>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B181" s="19"/>
+      <c r="B181" s="18"/>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="19"/>
+      <c r="B182" s="18"/>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B184" s="19"/>
+      <c r="B184" s="18"/>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="19"/>
+      <c r="B185" s="18"/>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B186" s="19"/>
+      <c r="B186" s="18"/>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="19"/>
+      <c r="B187" s="18"/>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B188" s="19"/>
+      <c r="B188" s="18"/>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="19"/>
+      <c r="B189" s="18"/>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="19"/>
+      <c r="B190" s="18"/>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="19"/>
+      <c r="B191" s="18"/>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="19"/>
+      <c r="B192" s="18"/>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="19"/>
+      <c r="B193" s="18"/>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B195" s="20"/>
+      <c r="B195" s="19"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B196" s="20"/>
+      <c r="B196" s="19"/>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="20"/>
+      <c r="B197" s="19"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B198" s="20"/>
+      <c r="B198" s="19"/>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B199" s="20"/>
+      <c r="B199" s="19"/>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B201" s="19"/>
+      <c r="B201" s="18"/>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B202" s="19"/>
+      <c r="B202" s="18"/>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B203" s="19"/>
+      <c r="B203" s="18"/>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B204" s="19"/>
+      <c r="B204" s="18"/>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B205" s="19"/>
+      <c r="B205" s="18"/>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B206" s="19"/>
+      <c r="B206" s="18"/>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B207" s="19"/>
+      <c r="B207" s="18"/>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B208" s="19"/>
+      <c r="B208" s="18"/>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B209" s="19"/>
+      <c r="B209" s="18"/>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B211" s="17"/>
+      <c r="B211" s="16"/>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B212" s="17"/>
+      <c r="B212" s="16"/>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B213" s="17"/>
+      <c r="B213" s="16"/>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B214" s="17"/>
+      <c r="B214" s="16"/>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B215" s="17"/>
+      <c r="B215" s="16"/>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B216" s="17"/>
+      <c r="B216" s="16"/>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B217" s="18"/>
+      <c r="B217" s="17"/>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B218" s="6"/>
+      <c r="B218" s="5"/>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B219" s="17"/>
+      <c r="B219" s="16"/>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B220" s="18"/>
+      <c r="B220" s="17"/>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B221" s="15"/>
+      <c r="B221" s="14"/>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B222" s="15"/>
+      <c r="B222" s="14"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B223" s="15"/>
+      <c r="B223" s="14"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B224" s="15"/>
+      <c r="B224" s="14"/>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B226" s="15"/>
+      <c r="B226" s="14"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B227" s="15"/>
+      <c r="B227" s="14"/>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B228" s="19"/>
+      <c r="B228" s="18"/>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B229" s="19"/>
+      <c r="B229" s="18"/>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B230" s="19"/>
+      <c r="B230" s="18"/>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B231" s="19"/>
+      <c r="B231" s="18"/>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B232" s="19"/>
+      <c r="B232" s="18"/>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B233" s="19"/>
+      <c r="B233" s="18"/>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B234" s="19"/>
+      <c r="B234" s="18"/>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B236" s="17"/>
+      <c r="B236" s="16"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B237" s="17"/>
+      <c r="B237" s="16"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B238" s="17"/>
+      <c r="B238" s="16"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B239" s="17"/>
+      <c r="B239" s="16"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B240" s="17"/>
+      <c r="B240" s="16"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B241" s="17"/>
+      <c r="B241" s="16"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B242" s="18"/>
+      <c r="B242" s="17"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B243" s="6"/>
+      <c r="B243" s="5"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B244" s="17"/>
+      <c r="B244" s="16"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B245" s="18"/>
+      <c r="B245" s="17"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B246" s="19"/>
+      <c r="B246" s="18"/>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B247" s="19"/>
+      <c r="B247" s="18"/>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B248" s="19"/>
+      <c r="B248" s="18"/>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B249" s="19"/>
+      <c r="B249" s="18"/>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B250" s="19"/>
+      <c r="B250" s="18"/>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B251" s="19"/>
+      <c r="B251" s="18"/>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B252" s="19"/>
+      <c r="B252" s="18"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B253" s="19"/>
+      <c r="B253" s="18"/>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B254" s="19"/>
+      <c r="B254" s="18"/>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B255" s="19"/>
+      <c r="B255" s="18"/>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B256" s="19"/>
+      <c r="B256" s="18"/>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B257" s="19"/>
+      <c r="B257" s="18"/>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B258" s="19"/>
+      <c r="B258" s="18"/>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B259" s="19"/>
+      <c r="B259" s="18"/>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B260" s="19"/>
+      <c r="B260" s="18"/>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B261" s="19"/>
+      <c r="B261" s="18"/>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B262" s="19"/>
+      <c r="B262" s="18"/>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B263" s="19"/>
+      <c r="B263" s="18"/>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B264" s="19"/>
+      <c r="B264" s="18"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B265" s="19"/>
+      <c r="B265" s="18"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B266" s="19"/>
+      <c r="B266" s="18"/>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B267" s="19"/>
+      <c r="B267" s="18"/>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B268" s="19"/>
+      <c r="B268" s="18"/>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B269" s="19"/>
+      <c r="B269" s="18"/>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B270" s="19"/>
+      <c r="B270" s="18"/>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B271" s="19"/>
+      <c r="B271" s="18"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B272" s="19"/>
+      <c r="B272" s="18"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B273" s="19"/>
+      <c r="B273" s="18"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B274" s="19"/>
+      <c r="B274" s="18"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B275" s="19"/>
+      <c r="B275" s="18"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B276" s="19"/>
+      <c r="B276" s="18"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B277" s="19"/>
+      <c r="B277" s="18"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B278" s="19"/>
+      <c r="B278" s="18"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B279" s="19"/>
+      <c r="B279" s="18"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B280" s="19"/>
+      <c r="B280" s="18"/>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B281" s="19"/>
+      <c r="B281" s="18"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B282" s="21"/>
+      <c r="B282" s="20"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B284" s="19"/>
+      <c r="B284" s="18"/>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B285" s="19"/>
+      <c r="B285" s="18"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B286" s="19"/>
+      <c r="B286" s="18"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B287" s="19"/>
+      <c r="B287" s="18"/>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B288" s="19"/>
+      <c r="B288" s="18"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B289" s="19"/>
+      <c r="B289" s="18"/>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B290" s="19"/>
+      <c r="B290" s="18"/>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B291" s="19"/>
+      <c r="B291" s="18"/>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B292" s="19"/>
+      <c r="B292" s="18"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B293" s="19"/>
+      <c r="B293" s="18"/>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B294" s="19"/>
+      <c r="B294" s="18"/>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B295" s="19"/>
+      <c r="B295" s="18"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B296" s="19"/>
+      <c r="B296" s="18"/>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B297" s="19"/>
+      <c r="B297" s="18"/>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B298" s="19"/>
+      <c r="B298" s="18"/>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B299" s="19"/>
+      <c r="B299" s="18"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B300" s="19"/>
+      <c r="B300" s="18"/>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B301" s="19"/>
+      <c r="B301" s="18"/>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B302" s="19"/>
+      <c r="B302" s="18"/>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B303" s="19"/>
+      <c r="B303" s="18"/>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B304" s="19"/>
+      <c r="B304" s="18"/>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B305" s="19"/>
+      <c r="B305" s="18"/>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B306" s="19"/>
+      <c r="B306" s="18"/>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B307" s="19"/>
+      <c r="B307" s="18"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B308" s="19"/>
+      <c r="B308" s="18"/>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B309" s="19"/>
+      <c r="B309" s="18"/>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B310" s="19"/>
+      <c r="B310" s="18"/>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B311" s="19"/>
+      <c r="B311" s="18"/>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B312" s="19"/>
+      <c r="B312" s="18"/>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B313" s="19"/>
+      <c r="B313" s="18"/>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B314" s="19"/>
+      <c r="B314" s="18"/>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B315" s="19"/>
+      <c r="B315" s="18"/>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B316" s="19"/>
+      <c r="B316" s="18"/>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B317" s="19"/>
+      <c r="B317" s="18"/>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B318" s="19"/>
+      <c r="B318" s="18"/>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B319" s="19"/>
+      <c r="B319" s="18"/>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B320" s="19"/>
+      <c r="B320" s="18"/>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B322" s="17"/>
+      <c r="B322" s="16"/>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B323" s="17"/>
+      <c r="B323" s="16"/>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B324" s="17"/>
+      <c r="B324" s="16"/>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B325" s="17"/>
+      <c r="B325" s="16"/>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B326" s="17"/>
+      <c r="B326" s="16"/>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B327" s="17"/>
+      <c r="B327" s="16"/>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B328" s="18"/>
+      <c r="B328" s="17"/>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B329" s="6"/>
+      <c r="B329" s="5"/>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B330" s="17"/>
+      <c r="B330" s="16"/>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B331" s="18"/>
+      <c r="B331" s="17"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D91"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.58"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="25" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="25" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="25" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D50" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D51" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="25" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D52" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="25" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D53" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="25" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D54" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="25" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D55" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D56" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D57" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D58" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D59" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="25" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D60" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D61" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D62" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D63" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D64" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D65" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D66" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="25" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D67" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D68" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="25" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D69" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D70" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D71" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D72" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D73" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D74" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D75" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D76" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D77" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D78" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D79" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="25" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D80" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D81" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="25" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D82" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="25" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D83" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="25" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D84" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="25" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D85" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="25" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D86" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="25" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D87" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D88" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="25" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D89" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="25" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D90" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="25" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D91" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/Products.xlsx
+++ b/assets/Products.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="104">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -54,9 +54,6 @@
     <t xml:space="preserve">PRODUCT_ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Batch Details</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pre-Manufacturing Check</t>
   </si>
   <si>
@@ -108,6 +105,9 @@
     <t xml:space="preserve">Ethanol Dissolution</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
     <t xml:space="preserve">Concentration</t>
   </si>
   <si>
@@ -217,6 +217,123 @@
   </si>
   <si>
     <t xml:space="preserve">Drying chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stepwise Operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distillation Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centrifuge Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying Chart Lot: 1 (Crop: I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLR Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying Chart Lot: 1 (Crop: II)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying Chart Lot: 1 (Crop: III)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-manufacturing Control &amp; Precautions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line Clearance Record - Reactor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water Quenching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line Clearance Record - Filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ist Water Wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIth Water Wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spin Drying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ist Ethanol Wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IInd Ethanol Wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Batch Quantities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity Obtained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCPs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCl Consumption Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crystallization and settling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtration &amp; Centrifuge Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-process Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material Used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stepwise Extraction Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methanol Extraction Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settling &amp; Layer Seperation Chart (Methanol Extraction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexane Wash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methanol Recovery from Spent Oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solvent Consumption Details</t>
   </si>
 </sst>
 </file>
@@ -227,7 +344,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -262,6 +379,25 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -277,7 +413,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -328,6 +464,41 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -354,7 +525,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -439,39 +610,135 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -737,7 +1004,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C331"/>
+  <dimension ref="A1:C326"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="11.53"/>
@@ -783,7 +1050,7 @@
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="4" t="n">
@@ -794,7 +1061,7 @@
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="4" t="n">
@@ -805,7 +1072,7 @@
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
@@ -816,7 +1083,7 @@
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
@@ -827,7 +1094,7 @@
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
@@ -839,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
@@ -849,8 +1116,8 @@
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>13</v>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
@@ -871,11 +1138,11 @@
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>19</v>
+      <c r="B12" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -883,7 +1150,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2</v>
@@ -893,8 +1160,8 @@
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>11</v>
+      <c r="B14" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2</v>
@@ -904,8 +1171,8 @@
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>12</v>
+      <c r="B15" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2</v>
@@ -915,8 +1182,8 @@
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>20</v>
+      <c r="B16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2</v>
@@ -926,8 +1193,8 @@
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>21</v>
+      <c r="B17" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2</v>
@@ -937,8 +1204,8 @@
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>22</v>
+      <c r="B18" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>2</v>
@@ -949,7 +1216,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>2</v>
@@ -959,8 +1226,8 @@
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>24</v>
+      <c r="B20" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2</v>
@@ -970,8 +1237,8 @@
       <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>25</v>
+      <c r="B21" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2</v>
@@ -982,7 +1249,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2</v>
@@ -993,7 +1260,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2</v>
@@ -1003,8 +1270,8 @@
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>16</v>
+      <c r="B24" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2</v>
@@ -1014,8 +1281,8 @@
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>17</v>
+      <c r="B25" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2</v>
@@ -1025,30 +1292,30 @@
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>18</v>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>19</v>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
+      <c r="B28" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3</v>
@@ -1058,8 +1325,8 @@
       <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
+      <c r="B29" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3</v>
@@ -1069,8 +1336,8 @@
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>12</v>
+      <c r="B30" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>3</v>
@@ -1080,8 +1347,8 @@
       <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>27</v>
+      <c r="B31" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>3</v>
@@ -1092,7 +1359,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3</v>
@@ -1103,7 +1370,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3</v>
@@ -1113,8 +1380,8 @@
       <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>29</v>
+      <c r="B34" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>3</v>
@@ -1124,8 +1391,8 @@
       <c r="A35" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>17</v>
+      <c r="B35" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>3</v>
@@ -1136,29 +1403,29 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>19</v>
+      <c r="B37" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
+      <c r="B38" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="C38" s="4" t="n">
         <v>4</v>
@@ -1168,8 +1435,8 @@
       <c r="A39" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>11</v>
+      <c r="B39" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>4</v>
@@ -1179,8 +1446,8 @@
       <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>12</v>
+      <c r="B40" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C40" s="4" t="n">
         <v>4</v>
@@ -1190,8 +1457,8 @@
       <c r="A41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>30</v>
+      <c r="B41" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>4</v>
@@ -1201,8 +1468,8 @@
       <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>31</v>
+      <c r="B42" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>4</v>
@@ -1212,8 +1479,8 @@
       <c r="A43" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>17</v>
+      <c r="B43" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>4</v>
@@ -1223,11 +1490,11 @@
       <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>32</v>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1235,21 +1502,21 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>19</v>
+      <c r="B46" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1257,7 +1524,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C47" s="4" t="n">
         <v>5</v>
@@ -1268,7 +1535,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>5</v>
@@ -1279,7 +1546,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>5</v>
@@ -1290,7 +1557,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>5</v>
@@ -1301,7 +1568,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C51" s="4" t="n">
         <v>5</v>
@@ -1312,7 +1579,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C52" s="4" t="n">
         <v>5</v>
@@ -1323,10 +1590,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1334,40 +1601,40 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>18</v>
+      <c r="B55" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>19</v>
+      <c r="B56" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>10</v>
+      <c r="B57" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>6</v>
@@ -1377,8 +1644,8 @@
       <c r="A58" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>11</v>
+      <c r="B58" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="C58" s="4" t="n">
         <v>6</v>
@@ -1388,8 +1655,8 @@
       <c r="A59" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>12</v>
+      <c r="B59" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C59" s="4" t="n">
         <v>6</v>
@@ -1399,8 +1666,8 @@
       <c r="A60" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>14</v>
+      <c r="B60" s="15" t="s">
+        <v>36</v>
       </c>
       <c r="C60" s="4" t="n">
         <v>6</v>
@@ -1410,8 +1677,8 @@
       <c r="A61" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>34</v>
+      <c r="B61" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="C61" s="4" t="n">
         <v>6</v>
@@ -1421,8 +1688,8 @@
       <c r="A62" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>16</v>
+      <c r="B62" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C62" s="4" t="n">
         <v>6</v>
@@ -1432,91 +1699,66 @@
       <c r="A63" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="15" t="s">
-        <v>35</v>
+      <c r="B63" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="C63" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>6</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="14"/>
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="14"/>
     </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="14"/>
+    </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="14"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="14"/>
-    </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="14"/>
+      <c r="B74" s="16"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="14"/>
+      <c r="B75" s="16"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="14"/>
+      <c r="B76" s="16"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="14"/>
+      <c r="B77" s="16"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="16"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="16"/>
@@ -1585,22 +1827,22 @@
       <c r="B100" s="16"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="16"/>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="16"/>
+      <c r="B101" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="16"/>
+      <c r="B103" s="14"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="16"/>
+      <c r="B104" s="14"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="16"/>
+      <c r="B105" s="14"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="17"/>
+      <c r="B106" s="14"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="14"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="14"/>
@@ -1704,20 +1946,20 @@
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="14"/>
     </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="14"/>
-    </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="14"/>
+      <c r="B143" s="18"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="14"/>
+      <c r="B144" s="18"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="14"/>
+      <c r="B145" s="18"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="14"/>
+      <c r="B146" s="18"/>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="18"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="18"/>
@@ -1737,9 +1979,6 @@
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="18"/>
     </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="18"/>
-    </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="18"/>
     </row>
@@ -1752,6 +1991,9 @@
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="18"/>
     </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="18"/>
+    </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="18"/>
     </row>
@@ -1773,9 +2015,6 @@
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="18"/>
     </row>
-    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="18"/>
-    </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B168" s="18"/>
     </row>
@@ -1788,6 +2027,9 @@
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B171" s="18"/>
     </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="18"/>
+    </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B173" s="18"/>
     </row>
@@ -1803,9 +2045,6 @@
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B177" s="18"/>
     </row>
-    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="18"/>
-    </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B179" s="18"/>
     </row>
@@ -1818,6 +2057,9 @@
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B182" s="18"/>
     </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B183" s="18"/>
+    </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B184" s="18"/>
     </row>
@@ -1833,35 +2075,35 @@
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B188" s="18"/>
     </row>
-    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="18"/>
-    </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="18"/>
+      <c r="B190" s="19"/>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="18"/>
+      <c r="B191" s="19"/>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="18"/>
+      <c r="B192" s="19"/>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="18"/>
-    </row>
-    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B195" s="19"/>
+      <c r="B193" s="19"/>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B194" s="19"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B196" s="19"/>
+      <c r="B196" s="18"/>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="19"/>
+      <c r="B197" s="18"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B198" s="19"/>
+      <c r="B198" s="18"/>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B199" s="19"/>
+      <c r="B199" s="18"/>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="18"/>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B201" s="18"/>
@@ -1875,50 +2117,47 @@
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B204" s="18"/>
     </row>
-    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B205" s="18"/>
-    </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B206" s="18"/>
+      <c r="B206" s="16"/>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B207" s="18"/>
+      <c r="B207" s="16"/>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B208" s="18"/>
+      <c r="B208" s="16"/>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B209" s="18"/>
+      <c r="B209" s="16"/>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="16"/>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B211" s="16"/>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B212" s="16"/>
+      <c r="B212" s="17"/>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B213" s="16"/>
+      <c r="B213" s="5"/>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B214" s="16"/>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B215" s="16"/>
+      <c r="B215" s="17"/>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B216" s="16"/>
+      <c r="B216" s="14"/>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B217" s="17"/>
+      <c r="B217" s="14"/>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B218" s="5"/>
+      <c r="B218" s="14"/>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B219" s="16"/>
-    </row>
-    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B220" s="17"/>
+      <c r="B219" s="14"/>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B221" s="14"/>
@@ -1927,16 +2166,19 @@
       <c r="B222" s="14"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B223" s="14"/>
+      <c r="B223" s="18"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B224" s="14"/>
+      <c r="B224" s="18"/>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B225" s="18"/>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B226" s="14"/>
+      <c r="B226" s="18"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B227" s="14"/>
+      <c r="B227" s="18"/>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="18"/>
@@ -1944,50 +2186,50 @@
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B229" s="18"/>
     </row>
-    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B230" s="18"/>
-    </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B231" s="18"/>
+      <c r="B231" s="16"/>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B232" s="18"/>
+      <c r="B232" s="16"/>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B233" s="18"/>
+      <c r="B233" s="16"/>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B234" s="18"/>
+      <c r="B234" s="16"/>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B235" s="16"/>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B236" s="16"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B237" s="16"/>
+      <c r="B237" s="17"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B238" s="16"/>
+      <c r="B238" s="5"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B239" s="16"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B240" s="16"/>
+      <c r="B240" s="17"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B241" s="16"/>
+      <c r="B241" s="18"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B242" s="17"/>
+      <c r="B242" s="18"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B243" s="5"/>
+      <c r="B243" s="18"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B244" s="16"/>
+      <c r="B244" s="18"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B245" s="17"/>
+      <c r="B245" s="18"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B246" s="18"/>
@@ -2083,10 +2325,7 @@
       <c r="B276" s="18"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B277" s="18"/>
-    </row>
-    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B278" s="18"/>
+      <c r="B277" s="20"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B279" s="18"/>
@@ -2098,7 +2337,10 @@
       <c r="B281" s="18"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B282" s="20"/>
+      <c r="B282" s="18"/>
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B283" s="18"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B284" s="18"/>
@@ -2196,50 +2438,35 @@
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B315" s="18"/>
     </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B316" s="18"/>
-    </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B317" s="18"/>
+      <c r="B317" s="16"/>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B318" s="18"/>
+      <c r="B318" s="16"/>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B319" s="18"/>
+      <c r="B319" s="16"/>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B320" s="18"/>
+      <c r="B320" s="16"/>
+    </row>
+    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B321" s="16"/>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B322" s="16"/>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B323" s="16"/>
+      <c r="B323" s="17"/>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B324" s="16"/>
+      <c r="B324" s="5"/>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B325" s="16"/>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B326" s="16"/>
-    </row>
-    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B327" s="16"/>
-    </row>
-    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B328" s="17"/>
-    </row>
-    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B329" s="5"/>
-    </row>
-    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B330" s="16"/>
-    </row>
-    <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B331" s="17"/>
+      <c r="B326" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2257,1286 +2484,3764 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D385"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.58"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="21" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="21" width="43.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="21" width="15.58"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="21" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="22" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="B4" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D4" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="B41" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B42" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B43" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="C45" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D47" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D49" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="C50" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="C51" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D55" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D57" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D59" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="D60" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="D61" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C62" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="D62" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D63" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D64" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D65" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D66" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="21" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D67" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D68" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D69" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C70" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D70" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C71" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D71" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D72" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C73" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D73" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="21" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D74" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="21" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D75" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D76" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C77" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D77" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D78" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D79" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="21" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D80" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D81" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="21" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D82" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C83" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D83" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C84" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D84" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C85" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D85" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C86" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D86" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D87" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="21" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C88" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D88" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="21" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C89" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D89" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="21" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C90" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D90" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D91" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="21" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C92" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D92" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="21" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D93" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="21" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="D94" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="21" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C95" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D95" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="21" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C96" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D96" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="21" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D97" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="21" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D98" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="21" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D99" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C100" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D100" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C101" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D101" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D102" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C103" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D103" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="21" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C104" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D104" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="21" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C105" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D105" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C106" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D106" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="21" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C107" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D107" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="21" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D108" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C109" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D109" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="21" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C110" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D110" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C111" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D111" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="21" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C112" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D112" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="21" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C113" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D113" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="21" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C114" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D114" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="21" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C115" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D115" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="21" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C116" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D116" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="21" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C117" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D117" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="21" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C118" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D118" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="21" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D119" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="21" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C120" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D120" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C121" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D121" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="21" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C122" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D122" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="21" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C123" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D123" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="21" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C124" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D124" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D125" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C126" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D126" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="21" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C127" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D127" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="21" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C128" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D128" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="21" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C129" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D129" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="21" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C130" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D130" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="21" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C131" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D131" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="21" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C132" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D132" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C133" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D133" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C134" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D134" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="21" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C135" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D135" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="21" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C136" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D136" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C137" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D137" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="21" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C138" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D138" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="21" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C139" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D139" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="21" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C140" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D140" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C141" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D141" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="21" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C142" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="D142" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="21" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C143" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="D143" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="21" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C144" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="D144" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="21" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C145" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D145" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="21" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C146" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D146" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C147" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D147" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C148" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D148" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="21" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C149" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D149" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="21" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C150" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D150" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C151" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D151" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="21" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C152" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D152" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C153" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D153" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="21" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C154" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D154" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="21" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C155" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D155" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="21" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C156" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D156" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="21" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C157" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D157" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C158" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D158" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="21" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C159" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D159" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="21" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C160" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D160" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="21" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C161" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D161" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="21" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C162" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="D162" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="21" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C163" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D163" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="21" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C164" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D164" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="21" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C165" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D165" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="21" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C166" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D166" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="21" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C167" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D167" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="21" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C168" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="D168" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="21" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C169" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D169" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="21" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C170" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D170" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C171" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D171" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="21" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D172" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="21" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C173" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D173" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="21" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C174" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="D174" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="21" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C175" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="D175" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="21" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C176" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="D176" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="21" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C177" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="D177" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="21" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C178" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="D178" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="21" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C179" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="D179" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="21" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C180" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D180" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="21" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C181" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D181" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="21" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C182" s="21" t="n">
         <v>44</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="D182" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="21" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C183" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="D183" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="21" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C184" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="D184" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="21" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C185" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="D185" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="21" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C186" s="21" t="n">
         <v>45</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="D186" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="21" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C187" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D187" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="21" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C188" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D188" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="21" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C189" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D189" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="21" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C190" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="D190" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="21" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="C191" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D191" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="21" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="C192" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D192" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="21" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="22" t="s">
+      <c r="C193" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="D193" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="21" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C194" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D194" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="21" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C195" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D195" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="23" t="s">
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="21" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C196" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D196" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="21" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C197" s="21" t="n">
         <v>47</v>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="23" t="s">
+      <c r="D197" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="21" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C198" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D198" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="21" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C199" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="D199" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="21" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C200" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="D200" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="21" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C201" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="D201" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="21" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C202" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="D202" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="21" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C203" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D203" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="21" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C204" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D204" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="21" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C205" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D205" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="21" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C206" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D206" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="21" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C207" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="D207" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="21" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C208" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="D208" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="21" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C209" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="D209" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="21" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C210" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="D210" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C211" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="D211" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="21" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C212" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="D212" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="21" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C213" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="D213" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="21" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C214" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="D214" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="21" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C215" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="D215" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="21" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C216" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D216" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="21" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C217" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D217" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="21" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C218" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D218" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="21" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C219" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D219" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="21" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C220" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D220" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="21" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C221" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="D221" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="21" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C222" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="D222" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="21" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C223" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="D223" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="21" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C224" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="D224" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="21" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C225" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="D225" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="21" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C226" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="D226" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="21" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C227" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="D227" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="21" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" s="4" t="n">
+      <c r="C228" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="D228" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="21" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C229" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="D229" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="21" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
+      <c r="C230" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="D230" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="21" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C231" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="D231" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="21" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C232" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="D232" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="21" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C233" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="D233" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="21" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C234" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="D234" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="21" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="C235" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="D235" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="21" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="C236" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="D236" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="21" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D41" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="25" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="25" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="25" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="25" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="25" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="25" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="25" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D49" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="25" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D50" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="25" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D51" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="25" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D52" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="25" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D53" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="25" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D54" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="25" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D55" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="25" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D56" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="25" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D57" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="25" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D58" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="25" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D59" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="25" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D60" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D61" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="25" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D62" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="25" t="n">
+      <c r="C237" s="21" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D63" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="25" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D64" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="25" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D65" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="25" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D66" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="25" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D67" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="25" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D68" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="25" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D69" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="25" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D70" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D71" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="25" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D72" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D73" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="25" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D74" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="25" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D75" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="25" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D76" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="25" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D77" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="25" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D78" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="25" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D79" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="25" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D80" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="25" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D81" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="25" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D82" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="25" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D83" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="25" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D84" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="25" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D85" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="25" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D86" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="25" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D87" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="25" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C88" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D88" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="25" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D89" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="25" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D90" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="25" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D91" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="D237" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B238" s="0"/>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B239" s="0"/>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B240" s="0"/>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B241" s="0"/>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B242" s="0"/>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B243" s="0"/>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B244" s="0"/>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B245" s="0"/>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B246" s="0"/>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B247" s="0"/>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B248" s="0"/>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B249" s="0"/>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B250" s="0"/>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B251" s="0"/>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B252" s="0"/>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B253" s="0"/>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B254" s="0"/>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B255" s="0"/>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B256" s="41"/>
+    </row>
+    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B257" s="41"/>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B258" s="41"/>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B259" s="41"/>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B260" s="41"/>
+    </row>
+    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B261" s="41"/>
+    </row>
+    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B262" s="41"/>
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B263" s="0"/>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B264" s="41"/>
+    </row>
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B265" s="41"/>
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B266" s="41"/>
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B267" s="41"/>
+    </row>
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B268" s="41"/>
+    </row>
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B269" s="41"/>
+    </row>
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B270" s="41"/>
+    </row>
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B271" s="0"/>
+    </row>
+    <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B272" s="42"/>
+    </row>
+    <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B273" s="42"/>
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B274" s="42"/>
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B275" s="42"/>
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B276" s="42"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B277" s="42"/>
+    </row>
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B278" s="42"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B279" s="0"/>
+    </row>
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B280" s="0"/>
+    </row>
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B281" s="0"/>
+    </row>
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B282" s="0"/>
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B283" s="0"/>
+    </row>
+    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B284" s="0"/>
+    </row>
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B285" s="0"/>
+    </row>
+    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B286" s="0"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B287" s="0"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B288" s="0"/>
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B289" s="0"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B290" s="0"/>
+    </row>
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B291" s="0"/>
+    </row>
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B292" s="0"/>
+    </row>
+    <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B293" s="0"/>
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B294" s="0"/>
+    </row>
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B295" s="0"/>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B296" s="43"/>
+    </row>
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B297" s="43"/>
+    </row>
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B298" s="43"/>
+    </row>
+    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B299" s="0"/>
+    </row>
+    <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B300" s="42"/>
+    </row>
+    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B301" s="44"/>
+    </row>
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B302" s="0"/>
+    </row>
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B303" s="42"/>
+    </row>
+    <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B304" s="42"/>
+    </row>
+    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B305" s="42"/>
+    </row>
+    <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B306" s="42"/>
+    </row>
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B307" s="42"/>
+    </row>
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B308" s="42"/>
+    </row>
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B309" s="42"/>
+    </row>
+    <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B310" s="42"/>
+    </row>
+    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B311" s="44"/>
+    </row>
+    <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B312" s="0"/>
+    </row>
+    <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B313" s="42"/>
+    </row>
+    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B314" s="42"/>
+    </row>
+    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B315" s="42"/>
+    </row>
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B316" s="42"/>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B317" s="42"/>
+    </row>
+    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B318" s="42"/>
+    </row>
+    <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B319" s="44"/>
+    </row>
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B320" s="0"/>
+    </row>
+    <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B321" s="0"/>
+    </row>
+    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B322" s="0"/>
+    </row>
+    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B323" s="0"/>
+    </row>
+    <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B324" s="0"/>
+    </row>
+    <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B325" s="0"/>
+    </row>
+    <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B326" s="0"/>
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B327" s="0"/>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B328" s="0"/>
+    </row>
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B329" s="0"/>
+    </row>
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B330" s="0"/>
+    </row>
+    <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B331" s="45"/>
+    </row>
+    <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B332" s="45"/>
+    </row>
+    <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B333" s="46"/>
+    </row>
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B334" s="0"/>
+    </row>
+    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B335" s="0"/>
+    </row>
+    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B336" s="0"/>
+    </row>
+    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B337" s="0"/>
+    </row>
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B338" s="0"/>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B339" s="0"/>
+    </row>
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B340" s="0"/>
+    </row>
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B341" s="0"/>
+    </row>
+    <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B342" s="41"/>
+    </row>
+    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B343" s="0"/>
+    </row>
+    <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B344" s="47"/>
+    </row>
+    <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B345" s="47"/>
+    </row>
+    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B346" s="47"/>
+    </row>
+    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B347" s="0"/>
+    </row>
+    <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B348" s="41"/>
+    </row>
+    <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B349" s="41"/>
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B350" s="0"/>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B351" s="48"/>
+    </row>
+    <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B352" s="48"/>
+    </row>
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B353" s="48"/>
+    </row>
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B354" s="48"/>
+    </row>
+    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B355" s="48"/>
+    </row>
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B356" s="48"/>
+    </row>
+    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B357" s="49"/>
+    </row>
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B358" s="0"/>
+    </row>
+    <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B359" s="0"/>
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B360" s="49"/>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B361" s="50"/>
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B362" s="50"/>
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B363" s="50"/>
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B364" s="50"/>
+    </row>
+    <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B366" s="51"/>
+    </row>
+    <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B367" s="51"/>
+    </row>
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B368" s="51"/>
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B369" s="51"/>
+    </row>
+    <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B370" s="51"/>
+    </row>
+    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B371" s="51"/>
+    </row>
+    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B372" s="51"/>
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B373" s="51"/>
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B374" s="51"/>
+    </row>
+    <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B376" s="52"/>
+    </row>
+    <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B377" s="52"/>
+    </row>
+    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B378" s="52"/>
+    </row>
+    <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B379" s="52"/>
+    </row>
+    <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B380" s="52"/>
+    </row>
+    <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B381" s="52"/>
+    </row>
+    <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B382" s="53"/>
+    </row>
+    <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B385" s="53"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/Products.xlsx
+++ b/assets/Products.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="272">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -334,6 +335,528 @@
   </si>
   <si>
     <t xml:space="preserve">Solvent Consumption Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTRUCTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB_STEP_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensure the area is cleaned as per SOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check electrical, purified water, steam for functioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment and utensils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensure cleanliness and labeling of all equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materials must be QC-approved before transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage of material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store in designated area with proper label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal protective equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use masks, gloves, head cap, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Instructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoid contamination, clean area post-activity, dispose waste per SOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wear PPE (mask &amp; gloves)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required during raw material handling and all manufacturing steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer tested &amp; approved raw materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move to staging area before dispensing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attach the dispensed material label along with record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispensing area should be clean and dry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleanliness of accessories and bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labels / records of previous batch removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poly bags lined waste bin should be clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty drums are removed from the area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check temperature, RH &amp; differential pressure working</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessories used for previous batch removed for cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raw material process order is authorized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status label of the product is present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log books updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weighing balance cleanliness &amp; calibration status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batch No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaned as per SOP No.: IB-MF-GEN-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference cleaning SOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaned By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment / Instrument Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment / Instrument ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature, RH &amp; Pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During line clearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line clearance Initiated by Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature &amp; Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line clearance Certified by QA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashwagandha Root</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purified Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispensing started at (date &amp; time):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date &amp; Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispensing completed at (date &amp; time):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark compliance with ✓ or NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulverizing area should be clean &amp; dry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleanliness of accessories and equipment parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous batch labels/records removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the temperature, RH &amp; differential pressure working</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaned as per SOP No.: IB-MF-GEN-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature, RH &amp; Differential Pressure at the time of Line clearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line clearance by Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line clearance certified by QA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check mesh integrity before start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulverize the material through 6 mm mesh. Check the mesh integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unload and note pulverized qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lot No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time From-To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty Charged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesh size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty Pulverized</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulverizing Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use protective gear for extraction process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counter-check material weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensure correct RM quantity charged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area clean and free from previous materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous batch labels/records removed &amp; relevent status labels are updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment log books updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extractor parts cleaned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaned as per SOP No.: IB-MF-GEN-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge 1500 KG Ashwagandha Root powder into the extractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge 6000 L of 70% Ethanol into the extractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Drain 50 L ethanol to verify bed level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise the temperature of the mass to about 65-70⁰C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⁰C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintain at 65-70⁰C for 3 hours &amp; filter. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeat the extraction for 3 times with 4500 L 70% ethanol for each extraction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take the fourth extract for counter current for next batch first extraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production executive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity of Ethanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh /Recovered (Quantity &amp; B No.) / CC (Quantity &amp; B No.) &amp; Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extraction Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ist Hr, Iind Hr &amp; IIIrd Hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtration Time From-To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miscellaneous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start blow off and collect the distillate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note the total quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unload the spent and clean the extractor as per SOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty of Aq. Solvent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment parts &amp; accessories cleaned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaned as per SOP No.: IB-MF-GEN-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge the filtrate into the evaporator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do charge each extract filtrate seperately</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate to 500L at 65-70°C under vaccum. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature should not cross &gt;70°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unload the mass and note down the qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmHg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty of Recovered Solvent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty of Semi Concentration Collected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KG/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaned as per SOP No.: IB-MF-GEN-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge the semi concentrate into the reactor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate to 75-80% TDS at 65-70°C under vaccum. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: Temperature should not cross &gt;70°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unload &amp; Note down the Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty of Concentration Collected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check &amp; transfer the extract to spray drying area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying area should be clean &amp; dry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleanliness of spray dryer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaned as per SOP No.: IB-MF-GEN-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge the material to the drier. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFED0000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dry at 65-70⁰C under vacuum for 10 hour, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">use VTD/TD/RCVD as applicable</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">note each hour temp &amp; vaccum in every hour and update on drying chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wet Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dried Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charged Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unload Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check mesh integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge the material into the Pulverize machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulverize the material through 0.5 mm mesh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Check the mesh integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total RM Used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Product Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QC Sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validation Sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stability Sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Others if any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferred Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total - sum(samples)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Output / Input) * 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Manager</t>
   </si>
 </sst>
 </file>
@@ -344,7 +867,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -398,8 +921,22 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFED0000"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3399FF"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,8 +949,20 @@
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -466,6 +1015,13 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
@@ -480,23 +1036,31 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
       <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color theme="0" tint="-0.35"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top/>
-      <bottom/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -525,7 +1089,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="78">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -658,71 +1222,59 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -742,6 +1294,114 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,7 +1415,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFED0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -792,8 +1452,8 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FFF2DCDB"/>
+      <rgbColor rgb="FF3399FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
@@ -4513,7 +5173,7 @@
       <c r="A145" s="21" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="34" t="s">
+      <c r="B145" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C145" s="21" t="n">
@@ -4527,7 +5187,7 @@
       <c r="A146" s="21" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="34" t="s">
+      <c r="B146" s="23" t="s">
         <v>40</v>
       </c>
       <c r="C146" s="21" t="n">
@@ -4541,7 +5201,7 @@
       <c r="A147" s="21" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="34" t="s">
+      <c r="B147" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C147" s="21" t="n">
@@ -4555,7 +5215,7 @@
       <c r="A148" s="21" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="34" t="s">
+      <c r="B148" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C148" s="21" t="n">
@@ -4569,7 +5229,7 @@
       <c r="A149" s="21" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="34" t="s">
+      <c r="B149" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C149" s="21" t="n">
@@ -4583,7 +5243,7 @@
       <c r="A150" s="21" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="34" t="s">
+      <c r="B150" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C150" s="21" t="n">
@@ -4597,7 +5257,7 @@
       <c r="A151" s="21" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="34" t="s">
+      <c r="B151" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C151" s="21" t="n">
@@ -4611,7 +5271,7 @@
       <c r="A152" s="21" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="35" t="s">
+      <c r="B152" s="34" t="s">
         <v>74</v>
       </c>
       <c r="C152" s="21" t="n">
@@ -4625,7 +5285,7 @@
       <c r="A153" s="21" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="34" t="s">
+      <c r="B153" s="23" t="s">
         <v>30</v>
       </c>
       <c r="C153" s="21" t="n">
@@ -4639,7 +5299,7 @@
       <c r="A154" s="21" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="36" t="s">
+      <c r="B154" s="27" t="s">
         <v>75</v>
       </c>
       <c r="C154" s="21" t="n">
@@ -4653,7 +5313,7 @@
       <c r="A155" s="21" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="37" t="s">
+      <c r="B155" s="35" t="s">
         <v>76</v>
       </c>
       <c r="C155" s="21" t="n">
@@ -4667,7 +5327,7 @@
       <c r="A156" s="21" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="37" t="s">
+      <c r="B156" s="35" t="s">
         <v>67</v>
       </c>
       <c r="C156" s="21" t="n">
@@ -4681,7 +5341,7 @@
       <c r="A157" s="21" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="37" t="s">
+      <c r="B157" s="35" t="s">
         <v>62</v>
       </c>
       <c r="C157" s="21" t="n">
@@ -4695,7 +5355,7 @@
       <c r="A158" s="21" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="37" t="s">
+      <c r="B158" s="35" t="s">
         <v>77</v>
       </c>
       <c r="C158" s="21" t="n">
@@ -4723,7 +5383,7 @@
       <c r="A160" s="21" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="37" t="s">
+      <c r="B160" s="35" t="s">
         <v>78</v>
       </c>
       <c r="C160" s="21" t="n">
@@ -4737,7 +5397,7 @@
       <c r="A161" s="21" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="37" t="s">
+      <c r="B161" s="35" t="s">
         <v>62</v>
       </c>
       <c r="C161" s="21" t="n">
@@ -4751,7 +5411,7 @@
       <c r="A162" s="21" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="37" t="s">
+      <c r="B162" s="35" t="s">
         <v>27</v>
       </c>
       <c r="C162" s="21" t="n">
@@ -4765,7 +5425,7 @@
       <c r="A163" s="21" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="36" t="s">
+      <c r="B163" s="27" t="s">
         <v>39</v>
       </c>
       <c r="C163" s="21" t="n">
@@ -4779,7 +5439,7 @@
       <c r="A164" s="21" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="34" t="s">
+      <c r="B164" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C164" s="21" t="n">
@@ -4793,7 +5453,7 @@
       <c r="A165" s="21" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="35" t="s">
+      <c r="B165" s="34" t="s">
         <v>74</v>
       </c>
       <c r="C165" s="21" t="n">
@@ -4807,7 +5467,7 @@
       <c r="A166" s="21" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="38" t="s">
+      <c r="B166" s="28" t="s">
         <v>79</v>
       </c>
       <c r="C166" s="21" t="n">
@@ -4821,7 +5481,7 @@
       <c r="A167" s="21" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="37" t="s">
+      <c r="B167" s="35" t="s">
         <v>80</v>
       </c>
       <c r="C167" s="21" t="n">
@@ -4835,7 +5495,7 @@
       <c r="A168" s="21" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="37" t="s">
+      <c r="B168" s="35" t="s">
         <v>81</v>
       </c>
       <c r="C168" s="21" t="n">
@@ -4849,7 +5509,7 @@
       <c r="A169" s="21" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="34" t="s">
+      <c r="B169" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C169" s="21" t="n">
@@ -4863,7 +5523,7 @@
       <c r="A170" s="21" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="34" t="s">
+      <c r="B170" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C170" s="21" t="n">
@@ -4877,7 +5537,7 @@
       <c r="A171" s="21" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="35" t="s">
+      <c r="B171" s="34" t="s">
         <v>41</v>
       </c>
       <c r="C171" s="21" t="n">
@@ -4891,7 +5551,7 @@
       <c r="A172" s="21" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="39" t="s">
+      <c r="B172" s="36" t="s">
         <v>16</v>
       </c>
       <c r="C172" s="21" t="n">
@@ -4905,7 +5565,7 @@
       <c r="A173" s="21" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="36" t="s">
+      <c r="B173" s="27" t="s">
         <v>52</v>
       </c>
       <c r="C173" s="21" t="n">
@@ -4919,7 +5579,7 @@
       <c r="A174" s="21" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="38" t="s">
+      <c r="B174" s="28" t="s">
         <v>53</v>
       </c>
       <c r="C174" s="21" t="n">
@@ -4933,7 +5593,7 @@
       <c r="A175" s="21" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="34" t="s">
+      <c r="B175" s="23" t="s">
         <v>82</v>
       </c>
       <c r="C175" s="21" t="n">
@@ -4947,7 +5607,7 @@
       <c r="A176" s="21" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="34" t="s">
+      <c r="B176" s="23" t="s">
         <v>83</v>
       </c>
       <c r="C176" s="21" t="n">
@@ -4961,7 +5621,7 @@
       <c r="A177" s="21" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="34" t="s">
+      <c r="B177" s="23" t="s">
         <v>54</v>
       </c>
       <c r="C177" s="21" t="n">
@@ -4975,7 +5635,7 @@
       <c r="A178" s="21" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="34" t="s">
+      <c r="B178" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C178" s="21" t="n">
@@ -4989,7 +5649,7 @@
       <c r="A179" s="21" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="34" t="s">
+      <c r="B179" s="23" t="s">
         <v>56</v>
       </c>
       <c r="C179" s="21" t="n">
@@ -5003,7 +5663,7 @@
       <c r="A180" s="21" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="34" t="s">
+      <c r="B180" s="23" t="s">
         <v>84</v>
       </c>
       <c r="C180" s="21" t="n">
@@ -5017,7 +5677,7 @@
       <c r="A181" s="21" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="34" t="s">
+      <c r="B181" s="23" t="s">
         <v>85</v>
       </c>
       <c r="C181" s="21" t="n">
@@ -5031,7 +5691,7 @@
       <c r="A182" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="34" t="s">
+      <c r="B182" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C182" s="21" t="n">
@@ -5045,7 +5705,7 @@
       <c r="A183" s="21" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="34" t="s">
+      <c r="B183" s="23" t="s">
         <v>40</v>
       </c>
       <c r="C183" s="21" t="n">
@@ -5059,7 +5719,7 @@
       <c r="A184" s="21" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="34" t="s">
+      <c r="B184" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C184" s="21" t="n">
@@ -5073,7 +5733,7 @@
       <c r="A185" s="21" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="34" t="s">
+      <c r="B185" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C185" s="21" t="n">
@@ -5087,7 +5747,7 @@
       <c r="A186" s="21" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="34" t="s">
+      <c r="B186" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C186" s="21" t="n">
@@ -5101,7 +5761,7 @@
       <c r="A187" s="21" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="34" t="s">
+      <c r="B187" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C187" s="21" t="n">
@@ -5115,7 +5775,7 @@
       <c r="A188" s="21" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="34" t="s">
+      <c r="B188" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C188" s="21" t="n">
@@ -5129,7 +5789,7 @@
       <c r="A189" s="21" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="34" t="s">
+      <c r="B189" s="23" t="s">
         <v>86</v>
       </c>
       <c r="C189" s="21" t="n">
@@ -5143,7 +5803,7 @@
       <c r="A190" s="21" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="34" t="s">
+      <c r="B190" s="23" t="s">
         <v>45</v>
       </c>
       <c r="C190" s="21" t="n">
@@ -5157,7 +5817,7 @@
       <c r="A191" s="21" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="34" t="s">
+      <c r="B191" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C191" s="21" t="n">
@@ -5171,7 +5831,7 @@
       <c r="A192" s="21" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="34" t="s">
+      <c r="B192" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C192" s="21" t="n">
@@ -5185,7 +5845,7 @@
       <c r="A193" s="21" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="34" t="s">
+      <c r="B193" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C193" s="21" t="n">
@@ -5199,7 +5859,7 @@
       <c r="A194" s="21" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="34" t="s">
+      <c r="B194" s="23" t="s">
         <v>65</v>
       </c>
       <c r="C194" s="21" t="n">
@@ -5213,7 +5873,7 @@
       <c r="A195" s="21" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="40" t="s">
+      <c r="B195" s="37" t="s">
         <v>46</v>
       </c>
       <c r="C195" s="21" t="n">
@@ -5227,7 +5887,7 @@
       <c r="A196" s="21" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="34" t="s">
+      <c r="B196" s="23" t="s">
         <v>87</v>
       </c>
       <c r="C196" s="21" t="n">
@@ -5241,7 +5901,7 @@
       <c r="A197" s="21" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="34" t="s">
+      <c r="B197" s="23" t="s">
         <v>88</v>
       </c>
       <c r="C197" s="21" t="n">
@@ -5255,7 +5915,7 @@
       <c r="A198" s="21" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="34" t="s">
+      <c r="B198" s="23" t="s">
         <v>89</v>
       </c>
       <c r="C198" s="21" t="n">
@@ -5269,7 +5929,7 @@
       <c r="A199" s="21" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="34" t="s">
+      <c r="B199" s="23" t="s">
         <v>90</v>
       </c>
       <c r="C199" s="21" t="n">
@@ -5283,7 +5943,7 @@
       <c r="A200" s="21" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="34" t="s">
+      <c r="B200" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C200" s="21" t="n">
@@ -5297,7 +5957,7 @@
       <c r="A201" s="21" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="34" t="s">
+      <c r="B201" s="23" t="s">
         <v>52</v>
       </c>
       <c r="C201" s="21" t="n">
@@ -5311,7 +5971,7 @@
       <c r="A202" s="21" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="34" t="s">
+      <c r="B202" s="23" t="s">
         <v>64</v>
       </c>
       <c r="C202" s="21" t="n">
@@ -5325,7 +5985,7 @@
       <c r="A203" s="21" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="34" t="s">
+      <c r="B203" s="23" t="s">
         <v>91</v>
       </c>
       <c r="C203" s="21" t="n">
@@ -5339,7 +5999,7 @@
       <c r="A204" s="21" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="34" t="s">
+      <c r="B204" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C204" s="21" t="n">
@@ -5353,7 +6013,7 @@
       <c r="A205" s="21" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="34" t="s">
+      <c r="B205" s="23" t="s">
         <v>93</v>
       </c>
       <c r="C205" s="21" t="n">
@@ -5367,7 +6027,7 @@
       <c r="A206" s="21" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="34" t="s">
+      <c r="B206" s="23" t="s">
         <v>94</v>
       </c>
       <c r="C206" s="21" t="n">
@@ -5381,7 +6041,7 @@
       <c r="A207" s="21" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="34" t="s">
+      <c r="B207" s="23" t="s">
         <v>95</v>
       </c>
       <c r="C207" s="21" t="n">
@@ -5395,7 +6055,7 @@
       <c r="A208" s="21" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="34" t="s">
+      <c r="B208" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C208" s="21" t="n">
@@ -5409,7 +6069,7 @@
       <c r="A209" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="34" t="s">
+      <c r="B209" s="23" t="s">
         <v>56</v>
       </c>
       <c r="C209" s="21" t="n">
@@ -5437,7 +6097,7 @@
       <c r="A211" s="21" t="n">
         <v>210</v>
       </c>
-      <c r="B211" s="34" t="s">
+      <c r="B211" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C211" s="21" t="n">
@@ -5451,7 +6111,7 @@
       <c r="A212" s="21" t="n">
         <v>211</v>
       </c>
-      <c r="B212" s="34" t="s">
+      <c r="B212" s="23" t="s">
         <v>40</v>
       </c>
       <c r="C212" s="21" t="n">
@@ -5465,7 +6125,7 @@
       <c r="A213" s="21" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="34" t="s">
+      <c r="B213" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C213" s="21" t="n">
@@ -5479,7 +6139,7 @@
       <c r="A214" s="21" t="n">
         <v>213</v>
       </c>
-      <c r="B214" s="34" t="s">
+      <c r="B214" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C214" s="21" t="n">
@@ -5493,7 +6153,7 @@
       <c r="A215" s="21" t="n">
         <v>214</v>
       </c>
-      <c r="B215" s="34" t="s">
+      <c r="B215" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C215" s="21" t="n">
@@ -5507,7 +6167,7 @@
       <c r="A216" s="21" t="n">
         <v>215</v>
       </c>
-      <c r="B216" s="34" t="s">
+      <c r="B216" s="23" t="s">
         <v>39</v>
       </c>
       <c r="C216" s="21" t="n">
@@ -5521,7 +6181,7 @@
       <c r="A217" s="21" t="n">
         <v>216</v>
       </c>
-      <c r="B217" s="34" t="s">
+      <c r="B217" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C217" s="21" t="n">
@@ -5535,7 +6195,7 @@
       <c r="A218" s="21" t="n">
         <v>217</v>
       </c>
-      <c r="B218" s="34" t="s">
+      <c r="B218" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C218" s="21" t="n">
@@ -5549,7 +6209,7 @@
       <c r="A219" s="21" t="n">
         <v>218</v>
       </c>
-      <c r="B219" s="34" t="s">
+      <c r="B219" s="23" t="s">
         <v>96</v>
       </c>
       <c r="C219" s="21" t="n">
@@ -5563,7 +6223,7 @@
       <c r="A220" s="21" t="n">
         <v>219</v>
       </c>
-      <c r="B220" s="36" t="s">
+      <c r="B220" s="27" t="s">
         <v>97</v>
       </c>
       <c r="C220" s="21" t="n">
@@ -5577,7 +6237,7 @@
       <c r="A221" s="21" t="n">
         <v>220</v>
       </c>
-      <c r="B221" s="37" t="s">
+      <c r="B221" s="35" t="s">
         <v>98</v>
       </c>
       <c r="C221" s="21" t="n">
@@ -5591,7 +6251,7 @@
       <c r="A222" s="21" t="n">
         <v>221</v>
       </c>
-      <c r="B222" s="36" t="s">
+      <c r="B222" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C222" s="21" t="n">
@@ -5605,7 +6265,7 @@
       <c r="A223" s="21" t="n">
         <v>222</v>
       </c>
-      <c r="B223" s="37" t="s">
+      <c r="B223" s="35" t="s">
         <v>49</v>
       </c>
       <c r="C223" s="21" t="n">
@@ -5619,7 +6279,7 @@
       <c r="A224" s="21" t="n">
         <v>223</v>
       </c>
-      <c r="B224" s="38" t="s">
+      <c r="B224" s="28" t="s">
         <v>50</v>
       </c>
       <c r="C224" s="21" t="n">
@@ -5633,7 +6293,7 @@
       <c r="A225" s="21" t="n">
         <v>224</v>
       </c>
-      <c r="B225" s="38" t="s">
+      <c r="B225" s="28" t="s">
         <v>51</v>
       </c>
       <c r="C225" s="21" t="n">
@@ -5647,7 +6307,7 @@
       <c r="A226" s="21" t="n">
         <v>225</v>
       </c>
-      <c r="B226" s="38" t="s">
+      <c r="B226" s="28" t="s">
         <v>99</v>
       </c>
       <c r="C226" s="21" t="n">
@@ -5661,7 +6321,7 @@
       <c r="A227" s="21" t="n">
         <v>226</v>
       </c>
-      <c r="B227" s="36" t="s">
+      <c r="B227" s="27" t="s">
         <v>67</v>
       </c>
       <c r="C227" s="21" t="n">
@@ -5675,7 +6335,7 @@
       <c r="A228" s="21" t="n">
         <v>227</v>
       </c>
-      <c r="B228" s="38" t="s">
+      <c r="B228" s="28" t="s">
         <v>16</v>
       </c>
       <c r="C228" s="21" t="n">
@@ -5689,7 +6349,7 @@
       <c r="A229" s="21" t="n">
         <v>228</v>
       </c>
-      <c r="B229" s="38" t="s">
+      <c r="B229" s="28" t="s">
         <v>100</v>
       </c>
       <c r="C229" s="21" t="n">
@@ -5703,7 +6363,7 @@
       <c r="A230" s="21" t="n">
         <v>229</v>
       </c>
-      <c r="B230" s="34" t="s">
+      <c r="B230" s="23" t="s">
         <v>36</v>
       </c>
       <c r="C230" s="21" t="n">
@@ -5717,7 +6377,7 @@
       <c r="A231" s="21" t="n">
         <v>230</v>
       </c>
-      <c r="B231" s="35" t="s">
+      <c r="B231" s="34" t="s">
         <v>101</v>
       </c>
       <c r="C231" s="21" t="n">
@@ -5731,7 +6391,7 @@
       <c r="A232" s="21" t="n">
         <v>231</v>
       </c>
-      <c r="B232" s="34" t="s">
+      <c r="B232" s="23" t="s">
         <v>102</v>
       </c>
       <c r="C232" s="21" t="n">
@@ -5745,7 +6405,7 @@
       <c r="A233" s="21" t="n">
         <v>232</v>
       </c>
-      <c r="B233" s="34" t="s">
+      <c r="B233" s="23" t="s">
         <v>82</v>
       </c>
       <c r="C233" s="21" t="n">
@@ -5759,7 +6419,7 @@
       <c r="A234" s="21" t="n">
         <v>233</v>
       </c>
-      <c r="B234" s="34" t="s">
+      <c r="B234" s="23" t="s">
         <v>103</v>
       </c>
       <c r="C234" s="21" t="n">
@@ -5773,7 +6433,7 @@
       <c r="A235" s="21" t="n">
         <v>234</v>
       </c>
-      <c r="B235" s="34" t="s">
+      <c r="B235" s="23" t="s">
         <v>54</v>
       </c>
       <c r="C235" s="21" t="n">
@@ -5787,7 +6447,7 @@
       <c r="A236" s="21" t="n">
         <v>235</v>
       </c>
-      <c r="B236" s="34" t="s">
+      <c r="B236" s="23" t="s">
         <v>55</v>
       </c>
       <c r="C236" s="21" t="n">
@@ -5801,7 +6461,7 @@
       <c r="A237" s="21" t="n">
         <v>236</v>
       </c>
-      <c r="B237" s="34" t="s">
+      <c r="B237" s="23" t="s">
         <v>56</v>
       </c>
       <c r="C237" s="21" t="n">
@@ -5812,436 +6472,436 @@
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B238" s="0"/>
+      <c r="B238" s="1"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B239" s="0"/>
+      <c r="B239" s="1"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B240" s="0"/>
+      <c r="B240" s="1"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B241" s="0"/>
+      <c r="B241" s="1"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B242" s="0"/>
+      <c r="B242" s="1"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B243" s="0"/>
+      <c r="B243" s="1"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B244" s="0"/>
+      <c r="B244" s="1"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B245" s="0"/>
+      <c r="B245" s="1"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B246" s="0"/>
+      <c r="B246" s="1"/>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B247" s="0"/>
+      <c r="B247" s="1"/>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B248" s="0"/>
+      <c r="B248" s="1"/>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B249" s="0"/>
+      <c r="B249" s="1"/>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B250" s="0"/>
+      <c r="B250" s="1"/>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B251" s="0"/>
+      <c r="B251" s="1"/>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B252" s="0"/>
+      <c r="B252" s="1"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B253" s="0"/>
+      <c r="B253" s="1"/>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B254" s="0"/>
+      <c r="B254" s="1"/>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B255" s="0"/>
+      <c r="B255" s="1"/>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B256" s="41"/>
+      <c r="B256" s="38"/>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B257" s="41"/>
+      <c r="B257" s="38"/>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B258" s="41"/>
+      <c r="B258" s="38"/>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B259" s="41"/>
+      <c r="B259" s="38"/>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B260" s="41"/>
+      <c r="B260" s="38"/>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B261" s="41"/>
+      <c r="B261" s="38"/>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B262" s="41"/>
+      <c r="B262" s="38"/>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B263" s="0"/>
+      <c r="B263" s="1"/>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B264" s="41"/>
+      <c r="B264" s="38"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B265" s="41"/>
+      <c r="B265" s="38"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B266" s="41"/>
+      <c r="B266" s="38"/>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B267" s="41"/>
+      <c r="B267" s="38"/>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B268" s="41"/>
+      <c r="B268" s="38"/>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B269" s="41"/>
+      <c r="B269" s="38"/>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B270" s="41"/>
+      <c r="B270" s="38"/>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B271" s="0"/>
+      <c r="B271" s="1"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B272" s="42"/>
+      <c r="B272" s="39"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B273" s="42"/>
+      <c r="B273" s="39"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B274" s="42"/>
+      <c r="B274" s="39"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B275" s="42"/>
+      <c r="B275" s="39"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B276" s="42"/>
+      <c r="B276" s="39"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B277" s="42"/>
+      <c r="B277" s="39"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B278" s="42"/>
+      <c r="B278" s="39"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B279" s="0"/>
+      <c r="B279" s="1"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B280" s="0"/>
+      <c r="B280" s="1"/>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B281" s="0"/>
+      <c r="B281" s="1"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B282" s="0"/>
+      <c r="B282" s="1"/>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B283" s="0"/>
+      <c r="B283" s="1"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B284" s="0"/>
+      <c r="B284" s="1"/>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B285" s="0"/>
+      <c r="B285" s="1"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B286" s="0"/>
+      <c r="B286" s="1"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B287" s="0"/>
+      <c r="B287" s="1"/>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B288" s="0"/>
+      <c r="B288" s="1"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B289" s="0"/>
+      <c r="B289" s="1"/>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B290" s="0"/>
+      <c r="B290" s="1"/>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B291" s="0"/>
+      <c r="B291" s="1"/>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B292" s="0"/>
+      <c r="B292" s="1"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B293" s="0"/>
+      <c r="B293" s="1"/>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B294" s="0"/>
+      <c r="B294" s="1"/>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B295" s="0"/>
+      <c r="B295" s="1"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B296" s="43"/>
+      <c r="B296" s="40"/>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B297" s="43"/>
+      <c r="B297" s="40"/>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B298" s="43"/>
+      <c r="B298" s="40"/>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B299" s="0"/>
+      <c r="B299" s="1"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B300" s="42"/>
+      <c r="B300" s="39"/>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B301" s="44"/>
+      <c r="B301" s="41"/>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B302" s="0"/>
+      <c r="B302" s="1"/>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B303" s="42"/>
+      <c r="B303" s="39"/>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B304" s="42"/>
+      <c r="B304" s="39"/>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B305" s="42"/>
+      <c r="B305" s="39"/>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B306" s="42"/>
+      <c r="B306" s="39"/>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B307" s="42"/>
+      <c r="B307" s="39"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B308" s="42"/>
+      <c r="B308" s="39"/>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B309" s="42"/>
+      <c r="B309" s="39"/>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B310" s="42"/>
+      <c r="B310" s="39"/>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B311" s="44"/>
+      <c r="B311" s="41"/>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B312" s="0"/>
+      <c r="B312" s="1"/>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B313" s="42"/>
+      <c r="B313" s="39"/>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B314" s="42"/>
+      <c r="B314" s="39"/>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B315" s="42"/>
+      <c r="B315" s="39"/>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B316" s="42"/>
+      <c r="B316" s="39"/>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B317" s="42"/>
+      <c r="B317" s="39"/>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B318" s="42"/>
+      <c r="B318" s="39"/>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B319" s="44"/>
+      <c r="B319" s="41"/>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B320" s="0"/>
+      <c r="B320" s="1"/>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B321" s="0"/>
+      <c r="B321" s="1"/>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B322" s="0"/>
+      <c r="B322" s="1"/>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B323" s="0"/>
+      <c r="B323" s="1"/>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B324" s="0"/>
+      <c r="B324" s="1"/>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B325" s="0"/>
+      <c r="B325" s="1"/>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B326" s="0"/>
+      <c r="B326" s="1"/>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B327" s="0"/>
+      <c r="B327" s="1"/>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B328" s="0"/>
+      <c r="B328" s="1"/>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B329" s="0"/>
+      <c r="B329" s="1"/>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B330" s="0"/>
+      <c r="B330" s="1"/>
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B331" s="45"/>
+      <c r="B331" s="42"/>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B332" s="45"/>
+      <c r="B332" s="42"/>
     </row>
     <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B333" s="46"/>
+      <c r="B333" s="43"/>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B334" s="0"/>
+      <c r="B334" s="1"/>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B335" s="0"/>
+      <c r="B335" s="1"/>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B336" s="0"/>
+      <c r="B336" s="1"/>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B337" s="0"/>
+      <c r="B337" s="1"/>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B338" s="0"/>
+      <c r="B338" s="1"/>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B339" s="0"/>
+      <c r="B339" s="1"/>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B340" s="0"/>
+      <c r="B340" s="1"/>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B341" s="0"/>
+      <c r="B341" s="1"/>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B342" s="41"/>
+      <c r="B342" s="38"/>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B343" s="0"/>
+      <c r="B343" s="1"/>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B344" s="47"/>
+      <c r="B344" s="44"/>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B345" s="47"/>
+      <c r="B345" s="44"/>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B346" s="47"/>
+      <c r="B346" s="44"/>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B347" s="0"/>
+      <c r="B347" s="1"/>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B348" s="41"/>
+      <c r="B348" s="38"/>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B349" s="41"/>
+      <c r="B349" s="38"/>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B350" s="0"/>
+      <c r="B350" s="1"/>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B351" s="48"/>
+      <c r="B351" s="45"/>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B352" s="48"/>
+      <c r="B352" s="45"/>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B353" s="48"/>
+      <c r="B353" s="45"/>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B354" s="48"/>
+      <c r="B354" s="45"/>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B355" s="48"/>
+      <c r="B355" s="45"/>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B356" s="48"/>
+      <c r="B356" s="45"/>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B357" s="49"/>
+      <c r="B357" s="46"/>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B358" s="0"/>
+      <c r="B358" s="1"/>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B359" s="0"/>
+      <c r="B359" s="1"/>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B360" s="49"/>
+      <c r="B360" s="46"/>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B361" s="50"/>
+      <c r="B361" s="47"/>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B362" s="50"/>
+      <c r="B362" s="47"/>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B363" s="50"/>
+      <c r="B363" s="47"/>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B364" s="50"/>
+      <c r="B364" s="47"/>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B366" s="51"/>
+      <c r="B366" s="48"/>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B367" s="51"/>
+      <c r="B367" s="48"/>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B368" s="51"/>
+      <c r="B368" s="48"/>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B369" s="51"/>
+      <c r="B369" s="48"/>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B370" s="51"/>
+      <c r="B370" s="48"/>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B371" s="51"/>
+      <c r="B371" s="48"/>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B372" s="51"/>
+      <c r="B372" s="48"/>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B373" s="51"/>
+      <c r="B373" s="48"/>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B374" s="51"/>
+      <c r="B374" s="48"/>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B376" s="52"/>
+      <c r="B376" s="49"/>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B377" s="52"/>
+      <c r="B377" s="49"/>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B378" s="52"/>
+      <c r="B378" s="49"/>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B379" s="52"/>
+      <c r="B379" s="49"/>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B380" s="52"/>
+      <c r="B380" s="49"/>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B381" s="52"/>
+      <c r="B381" s="49"/>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B382" s="53"/>
+      <c r="B382" s="50"/>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B385" s="53"/>
+      <c r="B385" s="50"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6252,4 +6912,4155 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F247"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="85.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="79.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.55"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="55"/>
+      <c r="E2" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="55"/>
+      <c r="E3" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="55"/>
+      <c r="E4" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="55"/>
+      <c r="E5" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="55"/>
+      <c r="E7" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="55"/>
+      <c r="E8" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="55"/>
+      <c r="E10" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="55"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="55"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="52" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="55"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="52" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="55"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="52" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="55"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="52" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="55"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="55"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="55"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="55"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="52" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="55"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="52" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="55"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="52" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="55"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="55"/>
+      <c r="E25" s="54" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="52" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="55"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="55"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="52" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="55"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="52" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="55"/>
+      <c r="E29" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="52" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" s="55"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="52" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="55"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="59"/>
+      <c r="F32" s="52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="52" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="59"/>
+      <c r="F33" s="52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="52" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="60" t="s">
+        <v>157</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="59"/>
+      <c r="F34" s="52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="52" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="61"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="52" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="52" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="61"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="52" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="52" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" s="55"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="52" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="52" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="55"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="52" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="52" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="55"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="52" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="55"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="52" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="55"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="52" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="55"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="52" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="55"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="52" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="55"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="52" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="55"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="52" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="55"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="52" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="55"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" s="55"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="52" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C49" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" s="55"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="52" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" s="55"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" s="55"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" s="55"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="55"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="52" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="55"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="52" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C55" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" s="55"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="52" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" s="55"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="52" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D57" s="55"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="52" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D58" s="55"/>
+      <c r="E58" s="62"/>
+      <c r="F58" s="52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="52" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59" s="55"/>
+      <c r="E59" s="62"/>
+      <c r="F59" s="52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="52" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E60" s="62"/>
+      <c r="F60" s="52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="52" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" s="65"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="52" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="63" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" s="65"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="52" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="65"/>
+      <c r="E63" s="66"/>
+      <c r="F63" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="52" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E64" s="66"/>
+      <c r="F64" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="52" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D65" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="E65" s="66"/>
+      <c r="F65" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="52" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C66" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E66" s="66"/>
+      <c r="F66" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="52" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C67" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D67" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E67" s="66"/>
+      <c r="F67" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="52" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C68" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="65"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="52" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" s="65"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="52" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D70" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="E70" s="66"/>
+      <c r="F70" s="52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="52" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C71" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D71" s="55"/>
+      <c r="E71" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="F71" s="52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="52" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C72" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D72" s="55"/>
+      <c r="E72" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F72" s="52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="52" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C73" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D73" s="55"/>
+      <c r="E73" s="56"/>
+      <c r="F73" s="52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="52" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C74" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D74" s="55"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="52" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="C75" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D75" s="55"/>
+      <c r="E75" s="56"/>
+      <c r="F75" s="52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="52" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C76" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D76" s="55"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="52" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C77" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D77" s="55"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="52" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D78" s="55"/>
+      <c r="E78" s="56"/>
+      <c r="F78" s="52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="52" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C79" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" s="55"/>
+      <c r="E79" s="56"/>
+      <c r="F79" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="52" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C80" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D80" s="55"/>
+      <c r="E80" s="56"/>
+      <c r="F80" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="52" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C81" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D81" s="55"/>
+      <c r="E81" s="56"/>
+      <c r="F81" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="52" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C82" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D82" s="55"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="52" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D83" s="55"/>
+      <c r="E83" s="56"/>
+      <c r="F83" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="52" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C84" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D84" s="55"/>
+      <c r="E84" s="56"/>
+      <c r="F84" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="52" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D85" s="55"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="52" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D86" s="55"/>
+      <c r="E86" s="56"/>
+      <c r="F86" s="52" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="52" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="C87" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E87" s="62"/>
+      <c r="F87" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="52" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D88" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E88" s="62" t="s">
+        <v>200</v>
+      </c>
+      <c r="F88" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="52" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D89" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E89" s="62"/>
+      <c r="F89" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="52" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="C90" s="54"/>
+      <c r="D90" s="55"/>
+      <c r="E90" s="54" t="s">
+        <v>204</v>
+      </c>
+      <c r="F90" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="52" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="C91" s="54"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="68" t="s">
+        <v>206</v>
+      </c>
+      <c r="F91" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="52" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92" s="55"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="52" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C93" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="D93" s="65"/>
+      <c r="E93" s="64"/>
+      <c r="F93" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="52" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C94" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D94" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="E94" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="F94" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="52" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="C95" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D95" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="E95" s="69" t="s">
+        <v>211</v>
+      </c>
+      <c r="F95" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="52" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="C96" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="D96" s="67"/>
+      <c r="E96" s="64"/>
+      <c r="F96" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="52" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C97" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D97" s="67"/>
+      <c r="E97" s="64"/>
+      <c r="F97" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="52" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C98" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="D98" s="67"/>
+      <c r="E98" s="66"/>
+      <c r="F98" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="52" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="C99" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="D99" s="65"/>
+      <c r="E99" s="66"/>
+      <c r="F99" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="52" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="C100" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D100" s="65"/>
+      <c r="E100" s="66"/>
+      <c r="F100" s="52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="52" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="C101" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D101" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E101" s="62"/>
+      <c r="F101" s="52" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="52" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="C102" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D102" s="58"/>
+      <c r="E102" s="62"/>
+      <c r="F102" s="52" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="52" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="C103" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D103" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E103" s="62"/>
+      <c r="F103" s="52" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="52" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C104" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D104" s="55"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="52" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="D105" s="55"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="52" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="C106" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D106" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E106" s="54"/>
+      <c r="F106" s="52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="52" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="C107" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D107" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E107" s="54"/>
+      <c r="F107" s="52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="52" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="C108" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D108" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="E108" s="54"/>
+      <c r="F108" s="52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="52" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C109" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D109" s="58"/>
+      <c r="E109" s="56"/>
+      <c r="F109" s="52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="52" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C110" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D110" s="58"/>
+      <c r="E110" s="56"/>
+      <c r="F110" s="52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="52" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C111" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D111" s="55"/>
+      <c r="E111" s="54"/>
+      <c r="F111" s="52" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="52" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C112" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D112" s="55"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="52" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="52" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C113" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D113" s="55"/>
+      <c r="E113" s="56"/>
+      <c r="F113" s="52" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="52" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C114" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D114" s="55"/>
+      <c r="E114" s="56"/>
+      <c r="F114" s="52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="52" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="C115" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D115" s="55"/>
+      <c r="E115" s="56"/>
+      <c r="F115" s="52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="52" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C116" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D116" s="55"/>
+      <c r="E116" s="56"/>
+      <c r="F116" s="52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="52" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="C117" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D117" s="55"/>
+      <c r="E117" s="56"/>
+      <c r="F117" s="52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="52" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C118" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D118" s="55"/>
+      <c r="E118" s="56"/>
+      <c r="F118" s="52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="52" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C119" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D119" s="55"/>
+      <c r="E119" s="56"/>
+      <c r="F119" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="52" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C120" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D120" s="55"/>
+      <c r="E120" s="56"/>
+      <c r="F120" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="52" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="C121" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D121" s="55"/>
+      <c r="E121" s="56"/>
+      <c r="F121" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="52" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C122" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D122" s="55"/>
+      <c r="E122" s="56"/>
+      <c r="F122" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="52" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C123" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D123" s="55"/>
+      <c r="E123" s="56"/>
+      <c r="F123" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="52" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D124" s="55"/>
+      <c r="E124" s="56"/>
+      <c r="F124" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="52" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C125" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D125" s="55"/>
+      <c r="E125" s="56"/>
+      <c r="F125" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="52" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C126" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D126" s="55"/>
+      <c r="E126" s="56"/>
+      <c r="F126" s="52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="52" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="C127" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D127" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E127" s="70" t="s">
+        <v>226</v>
+      </c>
+      <c r="F127" s="52" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="52" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="C128" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D128" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="E128" s="70" t="s">
+        <v>229</v>
+      </c>
+      <c r="F128" s="52" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="52" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="C129" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D129" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E129" s="62"/>
+      <c r="F129" s="52" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="52" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C130" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D130" s="55"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="52" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C131" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="D131" s="55"/>
+      <c r="E131" s="54"/>
+      <c r="F131" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="52" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="C132" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D132" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E132" s="54"/>
+      <c r="F132" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="52" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="C133" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D133" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="E133" s="54"/>
+      <c r="F133" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="52" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="C134" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D134" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="E134" s="54"/>
+      <c r="F134" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="52" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C135" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D135" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E135" s="54"/>
+      <c r="F135" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="52" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="C136" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D136" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="E136" s="54"/>
+      <c r="F136" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="52" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C137" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D137" s="55"/>
+      <c r="E137" s="54"/>
+      <c r="F137" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="52" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C138" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D138" s="55"/>
+      <c r="E138" s="54"/>
+      <c r="F138" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="52" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="C139" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D139" s="55"/>
+      <c r="E139" s="54"/>
+      <c r="F139" s="52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="52" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C140" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D140" s="55"/>
+      <c r="E140" s="54"/>
+      <c r="F140" s="52" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="52" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C141" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D141" s="55"/>
+      <c r="E141" s="54"/>
+      <c r="F141" s="52" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="52" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C142" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D142" s="55"/>
+      <c r="E142" s="56"/>
+      <c r="F142" s="52" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="52" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C143" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D143" s="55"/>
+      <c r="E143" s="56"/>
+      <c r="F143" s="52" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="52" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C144" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D144" s="55"/>
+      <c r="E144" s="56"/>
+      <c r="F144" s="52" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="52" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="C145" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D145" s="55"/>
+      <c r="E145" s="56"/>
+      <c r="F145" s="52" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="52" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C146" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D146" s="55"/>
+      <c r="E146" s="56"/>
+      <c r="F146" s="52" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="52" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C147" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D147" s="55"/>
+      <c r="E147" s="56"/>
+      <c r="F147" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="52" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C148" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D148" s="55"/>
+      <c r="E148" s="56"/>
+      <c r="F148" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="52" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C149" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D149" s="55"/>
+      <c r="E149" s="56"/>
+      <c r="F149" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="52" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C150" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D150" s="55"/>
+      <c r="E150" s="56"/>
+      <c r="F150" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="52" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C151" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D151" s="55"/>
+      <c r="E151" s="56"/>
+      <c r="F151" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="52" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C152" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D152" s="55"/>
+      <c r="E152" s="56"/>
+      <c r="F152" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="52" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C153" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D153" s="55"/>
+      <c r="E153" s="56"/>
+      <c r="F153" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="52" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C154" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D154" s="55"/>
+      <c r="E154" s="56"/>
+      <c r="F154" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="52" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="C155" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D155" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E155" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="F155" s="52" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="52" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="C156" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D156" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="E156" s="70" t="s">
+        <v>239</v>
+      </c>
+      <c r="F156" s="52" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="52" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="C157" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D157" s="55"/>
+      <c r="E157" s="62"/>
+      <c r="F157" s="52" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="52" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C158" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D158" s="55"/>
+      <c r="E158" s="54"/>
+      <c r="F158" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="52" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C159" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="D159" s="55"/>
+      <c r="E159" s="54"/>
+      <c r="F159" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="52" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="C160" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D160" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E160" s="54"/>
+      <c r="F160" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="52" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="C161" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D161" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="E161" s="54"/>
+      <c r="F161" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="52" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="C162" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D162" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="E162" s="54"/>
+      <c r="F162" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="52" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C163" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D163" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E163" s="54"/>
+      <c r="F163" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="52" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="C164" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D164" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="E164" s="54"/>
+      <c r="F164" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="52" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C165" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D165" s="55"/>
+      <c r="E165" s="54"/>
+      <c r="F165" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="52" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C166" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D166" s="55"/>
+      <c r="E166" s="54"/>
+      <c r="F166" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="52" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="C167" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D167" s="55"/>
+      <c r="E167" s="54"/>
+      <c r="F167" s="52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="52" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C168" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D168" s="55"/>
+      <c r="E168" s="54"/>
+      <c r="F168" s="52" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="52" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="C169" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D169" s="55"/>
+      <c r="E169" s="54"/>
+      <c r="F169" s="52" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="52" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C170" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D170" s="55"/>
+      <c r="E170" s="56"/>
+      <c r="F170" s="52" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="52" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="C171" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D171" s="55"/>
+      <c r="E171" s="56"/>
+      <c r="F171" s="52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="52" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="C172" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D172" s="55"/>
+      <c r="E172" s="56"/>
+      <c r="F172" s="52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="52" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C173" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D173" s="55"/>
+      <c r="E173" s="56"/>
+      <c r="F173" s="52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="52" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C174" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D174" s="55"/>
+      <c r="E174" s="56"/>
+      <c r="F174" s="52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="52" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="C175" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D175" s="55"/>
+      <c r="E175" s="56"/>
+      <c r="F175" s="52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="52" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C176" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D176" s="55"/>
+      <c r="E176" s="56"/>
+      <c r="F176" s="52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="52" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C177" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D177" s="55"/>
+      <c r="E177" s="56"/>
+      <c r="F177" s="52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="52" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C178" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D178" s="55"/>
+      <c r="E178" s="56"/>
+      <c r="F178" s="52" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="52" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C179" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D179" s="55"/>
+      <c r="E179" s="56"/>
+      <c r="F179" s="52" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="52" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C180" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D180" s="55"/>
+      <c r="E180" s="56"/>
+      <c r="F180" s="52" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="52" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C181" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D181" s="55"/>
+      <c r="E181" s="56"/>
+      <c r="F181" s="52" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="52" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C182" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D182" s="55"/>
+      <c r="E182" s="56"/>
+      <c r="F182" s="52" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="52" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C183" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D183" s="55"/>
+      <c r="E183" s="56"/>
+      <c r="F183" s="52" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="52" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="C184" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D184" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E184" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="F184" s="52" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="52" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="C185" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D185" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="E185" s="71"/>
+      <c r="F185" s="52" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="52" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C186" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D186" s="55"/>
+      <c r="E186" s="54"/>
+      <c r="F186" s="52" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="52" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="C187" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D187" s="55"/>
+      <c r="E187" s="54"/>
+      <c r="F187" s="52" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="52" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C188" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="D188" s="55"/>
+      <c r="E188" s="70" t="s">
+        <v>248</v>
+      </c>
+      <c r="F188" s="52" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="52" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C189" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D189" s="55"/>
+      <c r="E189" s="54"/>
+      <c r="F189" s="52" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="52" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="C190" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D190" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E190" s="54"/>
+      <c r="F190" s="52" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="52" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="C191" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D191" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E191" s="54"/>
+      <c r="F191" s="52" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="52" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="C192" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D192" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E192" s="54"/>
+      <c r="F192" s="52" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="52" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="63" t="s">
+        <v>251</v>
+      </c>
+      <c r="C193" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D193" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="E193" s="64"/>
+      <c r="F193" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="52" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="C194" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="D194" s="65"/>
+      <c r="E194" s="73"/>
+      <c r="F194" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="52" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C195" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="D195" s="74"/>
+      <c r="E195" s="75"/>
+      <c r="F195" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="52" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="C196" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D196" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="E196" s="75"/>
+      <c r="F196" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="52" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="C197" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D197" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="E197" s="77"/>
+      <c r="F197" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="52" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="C198" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D198" s="65"/>
+      <c r="E198" s="64"/>
+      <c r="F198" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="52" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C199" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="D199" s="65"/>
+      <c r="E199" s="64"/>
+      <c r="F199" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="52" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="C200" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="D200" s="65"/>
+      <c r="E200" s="64"/>
+      <c r="F200" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="52" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="63" t="s">
+        <v>253</v>
+      </c>
+      <c r="C201" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D201" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="E201" s="64"/>
+      <c r="F201" s="52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="52" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C202" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D202" s="55"/>
+      <c r="E202" s="68"/>
+      <c r="F202" s="52" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="52" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C203" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D203" s="55"/>
+      <c r="E203" s="56"/>
+      <c r="F203" s="52" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="52" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C204" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D204" s="55"/>
+      <c r="E204" s="56"/>
+      <c r="F204" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="52" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C205" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D205" s="55"/>
+      <c r="E205" s="56"/>
+      <c r="F205" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="52" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C206" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D206" s="55"/>
+      <c r="E206" s="56"/>
+      <c r="F206" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="52" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="C207" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D207" s="55"/>
+      <c r="E207" s="56"/>
+      <c r="F207" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="52" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C208" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D208" s="55"/>
+      <c r="E208" s="56"/>
+      <c r="F208" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="52" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="C209" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D209" s="55"/>
+      <c r="E209" s="56"/>
+      <c r="F209" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="52" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C210" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D210" s="55"/>
+      <c r="E210" s="56"/>
+      <c r="F210" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="52" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="C211" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D211" s="55"/>
+      <c r="E211" s="56"/>
+      <c r="F211" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="52" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C212" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D212" s="55"/>
+      <c r="E212" s="56"/>
+      <c r="F212" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="52" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C213" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D213" s="55"/>
+      <c r="E213" s="56"/>
+      <c r="F213" s="52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="52" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C214" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D214" s="55"/>
+      <c r="E214" s="56"/>
+      <c r="F214" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="52" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C215" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D215" s="55"/>
+      <c r="E215" s="56"/>
+      <c r="F215" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="52" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="C216" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D216" s="55"/>
+      <c r="E216" s="56"/>
+      <c r="F216" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="52" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="C217" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D217" s="55"/>
+      <c r="E217" s="56"/>
+      <c r="F217" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="52" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C218" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D218" s="55"/>
+      <c r="E218" s="56"/>
+      <c r="F218" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="52" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C219" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D219" s="55"/>
+      <c r="E219" s="56"/>
+      <c r="F219" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="52" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C220" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D220" s="55"/>
+      <c r="E220" s="56"/>
+      <c r="F220" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="52" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C221" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D221" s="55"/>
+      <c r="E221" s="56"/>
+      <c r="F221" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="52" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="C222" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D222" s="55"/>
+      <c r="E222" s="56"/>
+      <c r="F222" s="52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="52" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="C223" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D223" s="55"/>
+      <c r="E223" s="62"/>
+      <c r="F223" s="52" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="52" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="C224" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D224" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="E224" s="62"/>
+      <c r="F224" s="52" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="52" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="C225" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D225" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="E225" s="62" t="s">
+        <v>257</v>
+      </c>
+      <c r="F225" s="52" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="52" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C226" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D226" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E226" s="62"/>
+      <c r="F226" s="52" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="52" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="C227" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="D227" s="65"/>
+      <c r="E227" s="66"/>
+      <c r="F227" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="52" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="63" t="s">
+        <v>179</v>
+      </c>
+      <c r="C228" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D228" s="65"/>
+      <c r="E228" s="66"/>
+      <c r="F228" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="52" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C229" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="D229" s="65"/>
+      <c r="E229" s="66"/>
+      <c r="F229" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="52" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="C230" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D230" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E230" s="66"/>
+      <c r="F230" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="52" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C231" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D231" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="E231" s="66"/>
+      <c r="F231" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="52" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C232" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D232" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E232" s="66"/>
+      <c r="F232" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="52" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C233" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D233" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="E233" s="66"/>
+      <c r="F233" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="52" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C234" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D234" s="65"/>
+      <c r="E234" s="66"/>
+      <c r="F234" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="52" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="C235" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D235" s="65"/>
+      <c r="E235" s="66"/>
+      <c r="F235" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="52" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="C236" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D236" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="E236" s="66"/>
+      <c r="F236" s="52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="52" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="53" t="s">
+        <v>258</v>
+      </c>
+      <c r="C237" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D237" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E237" s="56"/>
+      <c r="F237" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="52" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="C238" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D238" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E238" s="56"/>
+      <c r="F238" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="52" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="C239" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D239" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E239" s="56"/>
+      <c r="F239" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="52" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="C240" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D240" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E240" s="56"/>
+      <c r="F240" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="52" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="C241" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="D241" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E241" s="56"/>
+      <c r="F241" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="52" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="C242" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D242" s="58"/>
+      <c r="E242" s="56"/>
+      <c r="F242" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="52" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="C243" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D243" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E243" s="70" t="s">
+        <v>266</v>
+      </c>
+      <c r="F243" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="52" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="C244" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D244" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="E244" s="70" t="s">
+        <v>268</v>
+      </c>
+      <c r="F244" s="52" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="52" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="C245" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D245" s="55"/>
+      <c r="E245" s="56"/>
+      <c r="F245" s="52" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="52" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="C246" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D246" s="55"/>
+      <c r="E246" s="56"/>
+      <c r="F246" s="52" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="52" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="53" t="s">
+        <v>271</v>
+      </c>
+      <c r="C247" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D247" s="55"/>
+      <c r="E247" s="56"/>
+      <c r="F247" s="52" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E195:E196"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>